--- a/epics/1118/validations/quality_report.xlsx
+++ b/epics/1118/validations/quality_report.xlsx
@@ -8,10 +8,17 @@
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="PROJECT" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="CALENDAR" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="CALENDAR" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="CALENDAR_rejected" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="PROJECT" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="PROJECT_rejected" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CALENDAR'!$A$1:$E$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CALENDAR_rejected'!$A$1:$H$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'PROJECT'!$A$1:$E$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PROJECT_rejected'!$A$1:$I$6</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -48,7 +55,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4E4"/>
       </patternFill>
     </fill>
     <fill>
@@ -474,7 +481,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-07T19:39:17Z</t>
+          <t>2026-06-07T20:21:20Z</t>
         </is>
       </c>
     </row>
@@ -486,7 +493,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -497,7 +504,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -561,58 +568,58 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>PROJECT</t>
+          <t>CALENDAR</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>proj_id, column1</t>
+          <t>test_id</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CALENDAR</t>
+          <t>PROJECT</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>test_id</t>
+          <t>proj_id, column1</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
@@ -620,7 +627,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>PROJECT - per file</t>
+          <t>CALENDAR - per file</t>
         </is>
       </c>
     </row>
@@ -644,21 +651,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PROJECT_data.xlsx</t>
+          <t>CALENDAR.xlsx</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15"/>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>CALENDAR - per file</t>
+          <t>PROJECT - per file</t>
         </is>
       </c>
     </row>
@@ -682,14 +689,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CALENDAR_data.xlsx</t>
+          <t>PROJECT.xlsx</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -703,11 +710,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -740,7 +747,108 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>pk_not_unique</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>40.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>proj_id</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>fk_not_found</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>20.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>proj_id</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nullable_violation</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>20.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>test_id</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>nullable_violation</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>20.00%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:E5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -751,11 +859,254 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="37" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Source File</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Source Row</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>test_id</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Offending Value</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>CALENDAR.xlsx</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>pk_not_unique</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>primary key must be unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>CALENDAR.xlsx</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>pk_not_unique</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>primary key must be unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>CALENDAR.xlsx</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>proj_id</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>fk_not_found</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>value must exist in PROJECT.proj_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CALENDAR.xlsx</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>&lt;missing&gt;</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>test_id</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>nullable_violation</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>value is required</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>CALENDAR.xlsx</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>proj_id</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>nullable_violation</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>value is required</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H6"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -788,7 +1139,374 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>pk_not_unique</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>40.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>column1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>nullable_violation</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>20.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>column3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>max_length_violation</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>20.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>proj_id</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>nullable_violation</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>20.00%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:E5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Source File</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Source Row</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>proj_id</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>column1</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Offending Value</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>PROJECT.xlsx</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>pk_not_unique</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>primary key must be unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>PROJECT.xlsx</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>pk_not_unique</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>primary key must be unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>PROJECT.xlsx</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>&lt;missing&gt;</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>proj_id</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>nullable_violation</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>value is required</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>PROJECT.xlsx</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>&lt;missing&gt;</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>column1</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>nullable_violation</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>value is required</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>PROJECT.xlsx</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>column3</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>max_length_violation</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>xxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxx</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>length &lt;= 384</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/epics/1118/validations/quality_report.xlsx
+++ b/epics/1118/validations/quality_report.xlsx
@@ -9,16 +9,9 @@
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="CALENDAR" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="CALENDAR_rejected" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="PROJECT" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="PROJECT_rejected" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="PROJECT" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CALENDAR'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CALENDAR_rejected'!$A$1:$H$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'PROJECT'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PROJECT_rejected'!$A$1:$I$6</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -55,7 +48,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4E4"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -481,7 +474,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-07T20:21:20Z</t>
+          <t>2026-06-07T20:52:21Z</t>
         </is>
       </c>
     </row>
@@ -493,7 +486,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -504,7 +497,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -583,14 +576,14 @@
         <v>5</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
@@ -612,14 +605,14 @@
         <v>5</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
@@ -658,7 +651,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15"/>
@@ -696,7 +689,7 @@
         <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -710,11 +703,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -747,108 +740,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>pk_not_unique</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>40.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>proj_id</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>fk_not_found</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>20.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>proj_id</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>nullable_violation</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>20.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>test_id</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>nullable_violation</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>20.00%</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -859,254 +751,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="37" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Source File</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Source Row</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>test_id</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Violation</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Offending Value</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>Expected</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CALENDAR.xlsx</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>pk_not_unique</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>primary key must be unique</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CALENDAR.xlsx</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>pk_not_unique</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>primary key must be unique</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CALENDAR.xlsx</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>proj_id</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>fk_not_found</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>999</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>value must exist in PROJECT.proj_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CALENDAR.xlsx</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>&lt;missing&gt;</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>test_id</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>nullable_violation</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>value is required</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CALENDAR.xlsx</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>proj_id</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>nullable_violation</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>value is required</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:H6"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -1139,374 +788,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>pk_not_unique</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>40.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>column1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>nullable_violation</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>20.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>column3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>max_length_violation</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>20.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>proj_id</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>nullable_violation</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>20.00%</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E5"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Source File</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Source Row</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>proj_id</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>column1</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Violation</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>Offending Value</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Expected</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>PROJECT.xlsx</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>pk_not_unique</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>primary key must be unique</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>PROJECT.xlsx</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>pk_not_unique</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>primary key must be unique</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>PROJECT.xlsx</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>&lt;missing&gt;</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>proj_id</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>nullable_violation</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>value is required</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>PROJECT.xlsx</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>&lt;missing&gt;</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>column1</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>nullable_violation</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>value is required</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>PROJECT.xlsx</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>column3</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>max_length_violation</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>xxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxx</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>length &lt;= 384</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:I6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/epics/1118/validations/quality_report.xlsx
+++ b/epics/1118/validations/quality_report.xlsx
@@ -474,7 +474,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-07T20:52:21Z</t>
+          <t>2026-06-07T21:51:55Z</t>
         </is>
       </c>
     </row>

--- a/epics/1118/validations/quality_report.xlsx
+++ b/epics/1118/validations/quality_report.xlsx
@@ -9,9 +9,16 @@
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="CALENDAR" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="PROJECT" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="CALENDAR_rejected" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="PROJECT" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="PROJECT_rejected" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CALENDAR'!$A$1:$E$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CALENDAR_rejected'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'PROJECT'!$A$1:$E$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PROJECT_rejected'!$A$1:$I$2</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,10 +41,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
-    <font>
-      <b val="1"/>
-      <i val="1"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -48,7 +51,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4E4"/>
       </patternFill>
     </fill>
     <fill>
@@ -69,14 +72,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -442,12 +444,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -474,7 +476,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-07T21:51:55Z</t>
+          <t>2026-06-07T22:18:21Z</t>
         </is>
       </c>
     </row>
@@ -486,7 +488,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -497,7 +499,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -570,20 +572,20 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
@@ -599,97 +601,21 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>CALENDAR - per file</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Source File</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Rows</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Violations</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CALENDAR.xlsx</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>5</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>PROJECT - per file</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Source File</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Rows</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Violations</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>PROJECT.xlsx</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>5</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
+          <t>0.00%</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -703,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -740,7 +666,33 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>no_input_files</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:E2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -751,7 +703,104 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Source File</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Source Row</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>test_id</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Offending Value</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>no_input_files</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>searched_base='C:\\Users\\viber\\Desktop\\Data Projects\\data-quality-project\\epics\\1118'; file_pattern='sample/PROJEKT*.xlsx'; resolved_pattern='sample/PROJEKT*.xlsx'; existing_top_level=['configs/', 'contracts/', 'docs/', 'sample/', 'sample_dirty/', 'sample_multi_sheet/', 'specs/', 'validations/']; existing_top_level_count=8; subdir_searched='sample'; existing_in_subdir=['CALENDAR.xlsx', 'PROJECT.xlsx']; existing_in_subdir_count=2</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>at least one file matching glob 'sample/PROJEKT*.xlsx' (resolved to 'sample/PROJEKT*.xlsx') under base "C:\Users\viber\Desktop\Data Projects\data-quality-project\epics\1118"</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -788,7 +837,137 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>no_input_files</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:E2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Source File</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Source Row</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>proj_id</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>column1</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Offending Value</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>no_input_files</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>searched_base='C:\\Users\\viber\\Desktop\\Data Projects\\data-quality-project\\epics\\1118'; file_pattern='sample/PROJEKT*.xlsx'; resolved_pattern='sample/PROJEKT*.xlsx'; existing_top_level=['configs/', 'contracts/', 'docs/', 'sample/', 'sample_dirty/', 'sample_multi_sheet/', 'specs/', 'validations/']; existing_top_level_count=8; subdir_searched='sample'; existing_in_subdir=['CALENDAR.xlsx', 'PROJECT.xlsx']; existing_in_subdir_count=2</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>at least one file matching glob 'sample/PROJEKT*.xlsx' (resolved to 'sample/PROJEKT*.xlsx') under base "C:\Users\viber\Desktop\Data Projects\data-quality-project\epics\1118"</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/epics/1118/validations/quality_report.xlsx
+++ b/epics/1118/validations/quality_report.xlsx
@@ -9,16 +9,9 @@
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="CALENDAR" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="CALENDAR_rejected" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="PROJECT" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="PROJECT_rejected" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="PROJECT" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CALENDAR'!$A$1:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CALENDAR_rejected'!$A$1:$H$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'PROJECT'!$A$1:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PROJECT_rejected'!$A$1:$I$2</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -26,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +34,10 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -51,7 +48,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4E4"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -72,13 +69,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -444,12 +442,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -476,7 +474,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-07T22:18:21Z</t>
+          <t>2026-06-07T22:58:58Z</t>
         </is>
       </c>
     </row>
@@ -488,7 +486,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -499,7 +497,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -572,20 +570,20 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
@@ -601,21 +599,97 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0.00%</t>
-        </is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>CALENDAR - per file</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Source File</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Rows</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Violations</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CALENDAR.xlsx</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>PROJECT - per file</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Source File</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Rows</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Violations</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PROJECT.xlsx</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -629,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -666,33 +740,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>no_input_files</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -703,104 +751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Source File</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Source Row</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>test_id</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Violation</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Offending Value</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>Expected</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>no_input_files</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>searched_base='C:\\Users\\viber\\Desktop\\Data Projects\\data-quality-project\\epics\\1118'; file_pattern='sample/PROJEKT*.xlsx'; resolved_pattern='sample/PROJEKT*.xlsx'; existing_top_level=['configs/', 'contracts/', 'docs/', 'sample/', 'sample_dirty/', 'sample_multi_sheet/', 'specs/', 'validations/']; existing_top_level_count=8; subdir_searched='sample'; existing_in_subdir=['CALENDAR.xlsx', 'PROJECT.xlsx']; existing_in_subdir_count=2</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>at least one file matching glob 'sample/PROJEKT*.xlsx' (resolved to 'sample/PROJEKT*.xlsx') under base "C:\Users\viber\Desktop\Data Projects\data-quality-project\epics\1118"</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:H2"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -837,137 +788,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>no_input_files</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E2"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Source File</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Source Row</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>proj_id</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>column1</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Violation</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>Offending Value</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Expected</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>no_input_files</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>searched_base='C:\\Users\\viber\\Desktop\\Data Projects\\data-quality-project\\epics\\1118'; file_pattern='sample/PROJEKT*.xlsx'; resolved_pattern='sample/PROJEKT*.xlsx'; existing_top_level=['configs/', 'contracts/', 'docs/', 'sample/', 'sample_dirty/', 'sample_multi_sheet/', 'specs/', 'validations/']; existing_top_level_count=8; subdir_searched='sample'; existing_in_subdir=['CALENDAR.xlsx', 'PROJECT.xlsx']; existing_in_subdir_count=2</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>at least one file matching glob 'sample/PROJEKT*.xlsx' (resolved to 'sample/PROJEKT*.xlsx') under base "C:\Users\viber\Desktop\Data Projects\data-quality-project\epics\1118"</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:I2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/epics/1118/validations/quality_report.xlsx
+++ b/epics/1118/validations/quality_report.xlsx
@@ -7,11 +7,18 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="CALENDAR" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="PROJECT" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Run" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Profile" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Checks" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="CALENDAR_rejected" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="PROJECT_rejected" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Checks'!$A$1:$C$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'CALENDAR_rejected'!$A$1:$G$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'PROJECT_rejected'!$A$1:$H$16</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,11 +39,16 @@
     </font>
     <font>
       <b val="1"/>
+      <i val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
       <b val="1"/>
-      <i val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="4">
@@ -48,7 +60,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4E4"/>
       </patternFill>
     </fill>
     <fill>
@@ -69,14 +81,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -442,16 +457,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,7 +484,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-07T22:58:58Z</t>
+          <t>2026-06-09T22:35:58Z</t>
         </is>
       </c>
     </row>
@@ -486,210 +496,110 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Errors</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
+          <t>Status reason</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>25 error(s) across 2 table(s)</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Warnings</t>
+          <t>Duration (ms)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Info</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7"/>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>oracle</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Checks enabled</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>boolean_coercion, column_missing, max_length, nullable, pk_uniqueness, type_coercion</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Files</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Total Rows</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Errors</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Warnings</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>% Clean</t>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Checks disabled</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>allowed_values, fk_existence, format, max_value, min_value, pattern, unique</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>CLI args</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>validate-data --epic 1118</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Contract versions</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>CALENDAR</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>test_id</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>PROJECT</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>proj_id, column1</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>CALENDAR - per file</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Source File</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Rows</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Violations</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CALENDAR.xlsx</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>5</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>PROJECT - per file</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Source File</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Rows</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Violations</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>PROJECT.xlsx</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>5</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -703,40 +613,262 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Violation Kind</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Rate</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Overall clean row %</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Errors</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Warnings</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Clean Rows</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Total Rows</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Errors</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Warnings</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>Clean Row %</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>Completeness</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>PK Uniqueness</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>CALENDAR</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>test_id</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>PROJECT</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>proj_id, column1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr"/>
+      <c r="C10" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J10" s="1" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="K10" s="1" t="inlineStr">
+        <is>
+          <t>100.0</t>
         </is>
       </c>
     </row>
@@ -751,44 +883,1657 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Table: CALENDAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Type Format</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Primary Key</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Foreign Key</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Null #</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Null %</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Distinct Values</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>test_id</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BINARY_DOUBLE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>oracle</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>columnX1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CHAR(1)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>oracle</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>columnX2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>oracle</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>columnX3</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>VARCHAR2(384 BYTE)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>oracle</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>columnX4</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>VARCHAR2(384 BYTE)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>oracle</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>proj_id</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>VARCHAR2(384 BYTE)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>oracle</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>column1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>VARCHAR2(40000 BYTE)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>oracle</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Table: PROJECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Type Format</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Primary Key</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Foreign Key</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Null #</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Null %</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Distinct Values</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>proj_id</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BINARY_DOUBLE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>oracle</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>column1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CHAR(1)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>oracle</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>column2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>oracle</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>column3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>VARCHAR2(384 BYTE)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>oracle</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>column4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>VARCHAR2(384 BYTE)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>oracle</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A11:I11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="74" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Violation kind</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>boolean_coercion</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Verify boolean cells use one of the target's accepted true/false tokens.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>boolean_coercion_violation</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>column_missing</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Verify every contract-declared column exists in the data file.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>column_missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>max_length</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Verify string fields stay within their declared max_length.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>max_length_violation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>nullable</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Verify required (non-nullable) fields have a value on every row.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>nullable_violation</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>pk_uniqueness</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Verify primary-key tuples are unique across rows.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>pk_not_unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>type_coercion</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Verify each value parses to the field's declared type.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>type_coercion_violation</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C7"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="66" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Source File</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>test_id</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>columnX1</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>columnX2</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CALENDAR.xlsx</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Type violation: boolean</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>one of: 0, 1, n, y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CALENDAR.xlsx</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2024-01-15T10:00:00</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Type violation: timestamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>valid TIMESTAMP (e.g. YYYY-MM-DD HH:MM:SS, DD-Mon-YYYY HH:MM:SS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CALENDAR.xlsx</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Type violation: boolean</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>one of: 0, 1, n, y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CALENDAR.xlsx</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2024-01-16T11:00:00</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Type violation: timestamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>valid TIMESTAMP (e.g. YYYY-MM-DD HH:MM:SS, DD-Mon-YYYY HH:MM:SS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CALENDAR.xlsx</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Type violation: boolean</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>one of: 0, 1, n, y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CALENDAR.xlsx</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2024-02-20T11:30:00</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Type violation: timestamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>valid TIMESTAMP (e.g. YYYY-MM-DD HH:MM:SS, DD-Mon-YYYY HH:MM:SS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CALENDAR.xlsx</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Type violation: boolean</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>one of: 0, 1, n, y</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CALENDAR.xlsx</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2024-03-25T14:45:00</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Type violation: timestamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>valid TIMESTAMP (e.g. YYYY-MM-DD HH:MM:SS, DD-Mon-YYYY HH:MM:SS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CALENDAR.xlsx</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Type violation: boolean</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>one of: 0, 1, n, y</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CALENDAR.xlsx</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2024-04-10T09:15:00</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Type violation: timestamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>valid TIMESTAMP (e.g. YYYY-MM-DD HH:MM:SS, DD-Mon-YYYY HH:MM:SS)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G11"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="66" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Violation Kind</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Rate</t>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Source File</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>proj_id</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>column1</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>column1</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>column2</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PROJECT.xlsx</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Type violation: boolean</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>one of: 0, 1, n, y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PROJECT.xlsx</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>(null)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Missing value</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PROJECT.xlsx</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2024-01-15T10:00:00</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Type violation: timestamp</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>valid TIMESTAMP (e.g. YYYY-MM-DD HH:MM:SS, DD-Mon-YYYY HH:MM:SS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PROJECT.xlsx</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Type violation: boolean</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>one of: 0, 1, n, y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PROJECT.xlsx</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>(null)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Missing value</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PROJECT.xlsx</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2024-01-16T11:00:00</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Type violation: timestamp</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>valid TIMESTAMP (e.g. YYYY-MM-DD HH:MM:SS, DD-Mon-YYYY HH:MM:SS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PROJECT.xlsx</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Type violation: boolean</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>one of: 0, 1, n, y</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PROJECT.xlsx</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>(null)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Missing value</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PROJECT.xlsx</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2024-02-20T11:30:00</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Type violation: timestamp</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>valid TIMESTAMP (e.g. YYYY-MM-DD HH:MM:SS, DD-Mon-YYYY HH:MM:SS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PROJECT.xlsx</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Type violation: boolean</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>one of: 0, 1, n, y</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PROJECT.xlsx</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>(null)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Missing value</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PROJECT.xlsx</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2024-03-25T14:45:00</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Type violation: timestamp</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>valid TIMESTAMP (e.g. YYYY-MM-DD HH:MM:SS, DD-Mon-YYYY HH:MM:SS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PROJECT.xlsx</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Type violation: boolean</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>one of: 0, 1, n, y</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PROJECT.xlsx</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>(null)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Missing value</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PROJECT.xlsx</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2024-04-10T09:15:00</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Type violation: timestamp</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>valid TIMESTAMP (e.g. YYYY-MM-DD HH:MM:SS, DD-Mon-YYYY HH:MM:SS)</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>